--- a/nriss-patch-2/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -846,7 +846,7 @@
     <t>The type of relationship this person has to the patient (father, mother, brother etc.).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-PersonalRelationshipRoleType-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-PersonalRelationshipRoleType-cisis|20260916095452</t>
   </si>
   <si>
     <t>code</t>
@@ -1118,7 +1118,7 @@
     <t>The actual condition specified. Could be a coded condition (like MI or Diabetes) or a less specific string like 'cancer' depending on how much is known about the condition and the capabilities of the creating system.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260916095457</t>
   </si>
   <si>
     <t>.value</t>
